--- a/Legenda.xlsx
+++ b/Legenda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMERSONJHONE_\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMERSONJHONE_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96870F47-51E1-4008-935B-D04834EE3F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C219D27-BAB2-4BCD-9807-67CECF1AD1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{B00CA4D1-2BF5-4D1E-9365-85E1E06E2E4C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="1257">
   <si>
     <t>HORARIO ROSTER</t>
   </si>
@@ -3793,6 +3793,9 @@
   </si>
   <si>
     <t>1830-2226_BR</t>
+  </si>
+  <si>
+    <t>T712</t>
   </si>
 </sst>
 </file>
@@ -4187,7 +4190,7 @@
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4201,7 +4204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -4215,7 +4218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -4229,7 +4232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -4243,7 +4246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -4271,7 +4274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -4285,7 +4288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -4299,7 +4302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -4313,7 +4316,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -4327,7 +4330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4341,7 +4344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -4355,7 +4358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -4369,7 +4372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
@@ -4383,7 +4386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -4397,7 +4400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>47</v>
       </c>
@@ -4411,7 +4414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>50</v>
       </c>
@@ -4425,7 +4428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
@@ -4439,7 +4442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
@@ -4453,7 +4456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -4467,7 +4470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
@@ -4481,7 +4484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>65</v>
       </c>
@@ -4495,7 +4498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>68</v>
       </c>
@@ -4509,7 +4512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>71</v>
       </c>
@@ -4523,7 +4526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>74</v>
       </c>
@@ -4537,7 +4540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>77</v>
       </c>
@@ -4551,7 +4554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
@@ -4565,7 +4568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>83</v>
       </c>
@@ -4579,7 +4582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>86</v>
       </c>
@@ -4593,7 +4596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>89</v>
       </c>
@@ -4607,7 +4610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>92</v>
       </c>
@@ -4621,7 +4624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>95</v>
       </c>
@@ -4635,7 +4638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>98</v>
       </c>
@@ -4649,7 +4652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>101</v>
       </c>
@@ -4663,7 +4666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>104</v>
       </c>
@@ -4677,7 +4680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>107</v>
       </c>
@@ -4691,7 +4694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>110</v>
       </c>
@@ -4705,7 +4708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>113</v>
       </c>
@@ -4719,7 +4722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>116</v>
       </c>
@@ -4733,7 +4736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
@@ -4747,7 +4750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -4761,7 +4764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>125</v>
       </c>
@@ -4775,7 +4778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -4789,7 +4792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>131</v>
       </c>
@@ -4803,7 +4806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>134</v>
       </c>
@@ -4817,7 +4820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>137</v>
       </c>
@@ -4831,7 +4834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>140</v>
       </c>
@@ -4845,7 +4848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>143</v>
       </c>
@@ -4859,7 +4862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>146</v>
       </c>
@@ -4873,7 +4876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>149</v>
       </c>
@@ -4887,7 +4890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>152</v>
       </c>
@@ -4901,7 +4904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>155</v>
       </c>
@@ -4915,7 +4918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>158</v>
       </c>
@@ -4929,7 +4932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>161</v>
       </c>
@@ -4943,7 +4946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>164</v>
       </c>
@@ -4957,7 +4960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>167</v>
       </c>
@@ -4971,7 +4974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>170</v>
       </c>
@@ -4985,7 +4988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>173</v>
       </c>
@@ -4999,7 +5002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>176</v>
       </c>
@@ -5013,7 +5016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>179</v>
       </c>
@@ -5027,7 +5030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>173</v>
       </c>
@@ -5041,7 +5044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>183</v>
       </c>
@@ -5055,7 +5058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>186</v>
       </c>
@@ -5069,7 +5072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>189</v>
       </c>
@@ -5083,7 +5086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>192</v>
       </c>
@@ -5097,7 +5100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>195</v>
       </c>
@@ -5111,7 +5114,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>199</v>
       </c>
@@ -5125,7 +5128,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>202</v>
       </c>
@@ -5139,7 +5142,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>205</v>
       </c>
@@ -5153,7 +5156,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>208</v>
       </c>
@@ -5167,7 +5170,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>208</v>
       </c>
@@ -5181,7 +5184,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>212</v>
       </c>
@@ -5195,7 +5198,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>215</v>
       </c>
@@ -5209,7 +5212,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>215</v>
       </c>
@@ -5223,7 +5226,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>219</v>
       </c>
@@ -5237,7 +5240,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>222</v>
       </c>
@@ -5251,7 +5254,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>225</v>
       </c>
@@ -5265,7 +5268,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>228</v>
       </c>
@@ -5279,7 +5282,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>231</v>
       </c>
@@ -5293,7 +5296,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>234</v>
       </c>
@@ -5307,7 +5310,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>237</v>
       </c>
@@ -5321,7 +5324,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>240</v>
       </c>
@@ -5335,7 +5338,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>243</v>
       </c>
@@ -5349,7 +5352,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>246</v>
       </c>
@@ -5363,7 +5366,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>249</v>
       </c>
@@ -5377,7 +5380,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>252</v>
       </c>
@@ -5391,7 +5394,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>255</v>
       </c>
@@ -5405,7 +5408,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>258</v>
       </c>
@@ -5419,7 +5422,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>261</v>
       </c>
@@ -5433,7 +5436,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>264</v>
       </c>
@@ -5447,7 +5450,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>267</v>
       </c>
@@ -5461,7 +5464,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>270</v>
       </c>
@@ -5475,7 +5478,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>273</v>
       </c>
@@ -5489,7 +5492,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>277</v>
       </c>
@@ -5503,7 +5506,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>280</v>
       </c>
@@ -5517,7 +5520,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>283</v>
       </c>
@@ -5531,7 +5534,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>286</v>
       </c>
@@ -5545,7 +5548,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>289</v>
       </c>
@@ -5559,7 +5562,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>292</v>
       </c>
@@ -5573,7 +5576,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>295</v>
       </c>
@@ -5587,7 +5590,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>298</v>
       </c>
@@ -5601,7 +5604,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>301</v>
       </c>
@@ -5615,7 +5618,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>304</v>
       </c>
@@ -5629,7 +5632,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>307</v>
       </c>
@@ -5643,7 +5646,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>310</v>
       </c>
@@ -5657,7 +5660,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>313</v>
       </c>
@@ -5671,7 +5674,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>316</v>
       </c>
@@ -5685,7 +5688,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>319</v>
       </c>
@@ -5699,7 +5702,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>322</v>
       </c>
@@ -5713,7 +5716,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>325</v>
       </c>
@@ -5727,7 +5730,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>328</v>
       </c>
@@ -5741,7 +5744,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>331</v>
       </c>
@@ -5755,7 +5758,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>334</v>
       </c>
@@ -5769,7 +5772,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>337</v>
       </c>
@@ -5783,7 +5786,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>340</v>
       </c>
@@ -5797,7 +5800,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>343</v>
       </c>
@@ -5811,7 +5814,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>346</v>
       </c>
@@ -5825,7 +5828,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>349</v>
       </c>
@@ -5839,7 +5842,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>352</v>
       </c>
@@ -5853,7 +5856,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>355</v>
       </c>
@@ -5867,7 +5870,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>358</v>
       </c>
@@ -5881,7 +5884,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>361</v>
       </c>
@@ -5895,7 +5898,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>364</v>
       </c>
@@ -5909,7 +5912,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>367</v>
       </c>
@@ -5923,7 +5926,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>370</v>
       </c>
@@ -5937,7 +5940,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>373</v>
       </c>
@@ -5951,7 +5954,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>373</v>
       </c>
@@ -5965,7 +5968,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>377</v>
       </c>
@@ -5979,7 +5982,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>380</v>
       </c>
@@ -5993,7 +5996,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>383</v>
       </c>
@@ -6007,7 +6010,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>386</v>
       </c>
@@ -6021,7 +6024,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>389</v>
       </c>
@@ -6035,7 +6038,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>392</v>
       </c>
@@ -6049,7 +6052,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>395</v>
       </c>
@@ -6063,7 +6066,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>398</v>
       </c>
@@ -6077,7 +6080,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>401</v>
       </c>
@@ -6091,7 +6094,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>404</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>407</v>
       </c>
@@ -6119,7 +6122,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>410</v>
       </c>
@@ -6133,7 +6136,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>413</v>
       </c>
@@ -6147,7 +6150,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>416</v>
       </c>
@@ -6161,7 +6164,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>420</v>
       </c>
@@ -6175,7 +6178,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>423</v>
       </c>
@@ -6189,7 +6192,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>426</v>
       </c>
@@ -6203,7 +6206,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>429</v>
       </c>
@@ -6217,7 +6220,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>432</v>
       </c>
@@ -6231,7 +6234,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>435</v>
       </c>
@@ -6245,7 +6248,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>438</v>
       </c>
@@ -6259,7 +6262,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>441</v>
       </c>
@@ -6273,7 +6276,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>444</v>
       </c>
@@ -6287,7 +6290,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>447</v>
       </c>
@@ -6301,7 +6304,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>450</v>
       </c>
@@ -6315,7 +6318,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>453</v>
       </c>
@@ -6329,7 +6332,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>456</v>
       </c>
@@ -6343,7 +6346,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>459</v>
       </c>
@@ -6357,7 +6360,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>462</v>
       </c>
@@ -6371,7 +6374,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>465</v>
       </c>
@@ -6385,7 +6388,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>468</v>
       </c>
@@ -6399,7 +6402,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>471</v>
       </c>
@@ -6413,7 +6416,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>474</v>
       </c>
@@ -6427,7 +6430,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>477</v>
       </c>
@@ -6441,7 +6444,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>480</v>
       </c>
@@ -6455,7 +6458,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>483</v>
       </c>
@@ -6469,7 +6472,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>486</v>
       </c>
@@ -6483,7 +6486,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>489</v>
       </c>
@@ -6497,7 +6500,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>492</v>
       </c>
@@ -6511,7 +6514,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>495</v>
       </c>
@@ -6525,7 +6528,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>498</v>
       </c>
@@ -6539,7 +6542,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>501</v>
       </c>
@@ -6553,7 +6556,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>504</v>
       </c>
@@ -6567,7 +6570,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>507</v>
       </c>
@@ -6581,7 +6584,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>510</v>
       </c>
@@ -6595,7 +6598,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>513</v>
       </c>
@@ -6609,7 +6612,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>516</v>
       </c>
@@ -6623,7 +6626,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>519</v>
       </c>
@@ -6637,7 +6640,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>522</v>
       </c>
@@ -6651,7 +6654,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>525</v>
       </c>
@@ -6665,7 +6668,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>528</v>
       </c>
@@ -6679,7 +6682,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>531</v>
       </c>
@@ -6693,7 +6696,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>534</v>
       </c>
@@ -6707,7 +6710,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>537</v>
       </c>
@@ -6721,7 +6724,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>540</v>
       </c>
@@ -6735,7 +6738,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>543</v>
       </c>
@@ -6749,7 +6752,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>546</v>
       </c>
@@ -6763,7 +6766,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>549</v>
       </c>
@@ -6777,7 +6780,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>552</v>
       </c>
@@ -6791,7 +6794,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>555</v>
       </c>
@@ -6805,7 +6808,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>558</v>
       </c>
@@ -6819,7 +6822,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>561</v>
       </c>
@@ -6833,7 +6836,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>564</v>
       </c>
@@ -6847,7 +6850,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>567</v>
       </c>
@@ -6861,7 +6864,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>570</v>
       </c>
@@ -6875,7 +6878,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>573</v>
       </c>
@@ -6889,7 +6892,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>576</v>
       </c>
@@ -6903,7 +6906,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>579</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>582</v>
       </c>
@@ -6931,7 +6934,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>585</v>
       </c>
@@ -6945,7 +6948,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>588</v>
       </c>
@@ -6959,7 +6962,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>591</v>
       </c>
@@ -6973,7 +6976,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>594</v>
       </c>
@@ -6987,7 +6990,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>597</v>
       </c>
@@ -7001,7 +7004,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>600</v>
       </c>
@@ -7015,7 +7018,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>603</v>
       </c>
@@ -7029,7 +7032,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>606</v>
       </c>
@@ -7057,7 +7060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>612</v>
       </c>
@@ -7071,7 +7074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>615</v>
       </c>
@@ -7085,7 +7088,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>615</v>
       </c>
@@ -7099,7 +7102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>619</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>622</v>
       </c>
@@ -7127,7 +7130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>625</v>
       </c>
@@ -7141,7 +7144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>628</v>
       </c>
@@ -7155,7 +7158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>631</v>
       </c>
@@ -7169,7 +7172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>634</v>
       </c>
@@ -7183,7 +7186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>637</v>
       </c>
@@ -7197,7 +7200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>640</v>
       </c>
@@ -7211,7 +7214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>643</v>
       </c>
@@ -7225,7 +7228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>646</v>
       </c>
@@ -7239,7 +7242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>649</v>
       </c>
@@ -7253,7 +7256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>652</v>
       </c>
@@ -7267,7 +7270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>655</v>
       </c>
@@ -7281,7 +7284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>658</v>
       </c>
@@ -7295,7 +7298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>661</v>
       </c>
@@ -7309,7 +7312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>664</v>
       </c>
@@ -7323,7 +7326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>667</v>
       </c>
@@ -7337,7 +7340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>670</v>
       </c>
@@ -7351,7 +7354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>673</v>
       </c>
@@ -7365,7 +7368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>676</v>
       </c>
@@ -7379,7 +7382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>679</v>
       </c>
@@ -7393,7 +7396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>682</v>
       </c>
@@ -7407,7 +7410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>685</v>
       </c>
@@ -7421,7 +7424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>688</v>
       </c>
@@ -7435,7 +7438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>691</v>
       </c>
@@ -7449,7 +7452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>694</v>
       </c>
@@ -7463,7 +7466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>697</v>
       </c>
@@ -7477,7 +7480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>700</v>
       </c>
@@ -7491,7 +7494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>703</v>
       </c>
@@ -7505,7 +7508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>706</v>
       </c>
@@ -7519,7 +7522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>609</v>
       </c>
@@ -7533,7 +7536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>711</v>
       </c>
@@ -7547,7 +7550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>714</v>
       </c>
@@ -7561,7 +7564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>717</v>
       </c>
@@ -7575,7 +7578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>720</v>
       </c>
@@ -7589,7 +7592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>723</v>
       </c>
@@ -7603,7 +7606,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>726</v>
       </c>
@@ -7617,7 +7620,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>729</v>
       </c>
@@ -7631,7 +7634,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>732</v>
       </c>
@@ -7645,7 +7648,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>735</v>
       </c>
@@ -7659,7 +7662,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>738</v>
       </c>
@@ -7673,7 +7676,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>741</v>
       </c>
@@ -7687,7 +7690,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>744</v>
       </c>
@@ -7701,7 +7704,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>747</v>
       </c>
@@ -7715,7 +7718,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>750</v>
       </c>
@@ -7729,7 +7732,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>753</v>
       </c>
@@ -7743,7 +7746,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>756</v>
       </c>
@@ -7757,7 +7760,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>759</v>
       </c>
@@ -7771,7 +7774,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>762</v>
       </c>
@@ -7785,7 +7788,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>765</v>
       </c>
@@ -7799,7 +7802,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>768</v>
       </c>
@@ -7813,7 +7816,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>771</v>
       </c>
@@ -7827,7 +7830,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>774</v>
       </c>
@@ -7841,7 +7844,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>777</v>
       </c>
@@ -7855,7 +7858,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>780</v>
       </c>
@@ -7869,7 +7872,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>783</v>
       </c>
@@ -7883,7 +7886,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>786</v>
       </c>
@@ -7897,7 +7900,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>789</v>
       </c>
@@ -7911,7 +7914,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>792</v>
       </c>
@@ -7925,7 +7928,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>795</v>
       </c>
@@ -7939,7 +7942,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>798</v>
       </c>
@@ -7953,7 +7956,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>801</v>
       </c>
@@ -7967,7 +7970,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>804</v>
       </c>
@@ -7981,7 +7984,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>807</v>
       </c>
@@ -7995,7 +7998,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>810</v>
       </c>
@@ -8009,7 +8012,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>813</v>
       </c>
@@ -8023,7 +8026,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>816</v>
       </c>
@@ -8037,7 +8040,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>819</v>
       </c>
@@ -8051,7 +8054,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>822</v>
       </c>
@@ -8065,7 +8068,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>825</v>
       </c>
@@ -8079,7 +8082,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>828</v>
       </c>
@@ -8093,7 +8096,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>831</v>
       </c>
@@ -8107,7 +8110,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>834</v>
       </c>
@@ -8121,7 +8124,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>837</v>
       </c>
@@ -8135,7 +8138,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>840</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>843</v>
       </c>
@@ -8163,7 +8166,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>846</v>
       </c>
@@ -8177,7 +8180,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>849</v>
       </c>
@@ -8191,7 +8194,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>852</v>
       </c>
@@ -8205,7 +8208,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>855</v>
       </c>
@@ -8219,7 +8222,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>858</v>
       </c>
@@ -8233,7 +8236,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>861</v>
       </c>
@@ -8247,7 +8250,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>864</v>
       </c>
@@ -8261,7 +8264,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>867</v>
       </c>
@@ -8275,7 +8278,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>870</v>
       </c>
@@ -8289,7 +8292,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>873</v>
       </c>
@@ -8303,7 +8306,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>876</v>
       </c>
@@ -8317,7 +8320,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>879</v>
       </c>
@@ -8331,7 +8334,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>882</v>
       </c>
@@ -8345,7 +8348,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>885</v>
       </c>
@@ -8359,7 +8362,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>888</v>
       </c>
@@ -8373,7 +8376,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>891</v>
       </c>
@@ -8387,7 +8390,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>894</v>
       </c>
@@ -8401,7 +8404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>897</v>
       </c>
@@ -8415,7 +8418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>897</v>
       </c>
@@ -8429,7 +8432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>902</v>
       </c>
@@ -8439,7 +8442,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>903</v>
       </c>
@@ -8449,7 +8452,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>904</v>
       </c>
@@ -8459,7 +8462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>905</v>
       </c>
@@ -8469,7 +8472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>894</v>
       </c>
@@ -8483,7 +8486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>897</v>
       </c>
@@ -8497,7 +8500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>910</v>
       </c>
@@ -8511,7 +8514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>897</v>
       </c>
@@ -8525,7 +8528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>914</v>
       </c>
@@ -8539,7 +8542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>176</v>
       </c>
@@ -8553,7 +8556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>919</v>
       </c>
@@ -8567,7 +8570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>919</v>
       </c>
@@ -8581,7 +8584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>176</v>
       </c>
@@ -8595,7 +8598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>926</v>
       </c>
@@ -8609,7 +8612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>929</v>
       </c>
@@ -8623,7 +8626,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>932</v>
       </c>
@@ -8637,7 +8640,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>935</v>
       </c>
@@ -8651,7 +8654,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>938</v>
       </c>
@@ -8665,7 +8668,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>4</v>
       </c>
@@ -8679,7 +8682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>8</v>
       </c>
@@ -8693,7 +8696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>11</v>
       </c>
@@ -8707,7 +8710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>14</v>
       </c>
@@ -8721,7 +8724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>17</v>
       </c>
@@ -8735,7 +8738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>20</v>
       </c>
@@ -8749,7 +8752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>23</v>
       </c>
@@ -8763,7 +8766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>26</v>
       </c>
@@ -8777,7 +8780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>29</v>
       </c>
@@ -8791,7 +8794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>32</v>
       </c>
@@ -8805,7 +8808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>35</v>
       </c>
@@ -8819,7 +8822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>38</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>41</v>
       </c>
@@ -8847,7 +8850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>44</v>
       </c>
@@ -8861,7 +8864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>941</v>
       </c>
@@ -8875,7 +8878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>944</v>
       </c>
@@ -8889,7 +8892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>47</v>
       </c>
@@ -8903,7 +8906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>50</v>
       </c>
@@ -8917,7 +8920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>53</v>
       </c>
@@ -8931,7 +8934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>947</v>
       </c>
@@ -8945,7 +8948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>950</v>
       </c>
@@ -8959,7 +8962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>953</v>
       </c>
@@ -8973,7 +8976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>956</v>
       </c>
@@ -8987,7 +8990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>959</v>
       </c>
@@ -9001,7 +9004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>962</v>
       </c>
@@ -9015,7 +9018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>965</v>
       </c>
@@ -9029,7 +9032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>968</v>
       </c>
@@ -9043,7 +9046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>971</v>
       </c>
@@ -9057,7 +9060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>974</v>
       </c>
@@ -9071,7 +9074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>977</v>
       </c>
@@ -9085,7 +9088,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>980</v>
       </c>
@@ -9099,7 +9102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>983</v>
       </c>
@@ -9113,7 +9116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>986</v>
       </c>
@@ -9127,7 +9130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>56</v>
       </c>
@@ -9141,7 +9144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>59</v>
       </c>
@@ -9155,7 +9158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>62</v>
       </c>
@@ -9169,7 +9172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>65</v>
       </c>
@@ -9183,7 +9186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>68</v>
       </c>
@@ -9197,7 +9200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>71</v>
       </c>
@@ -9211,7 +9214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>74</v>
       </c>
@@ -9225,7 +9228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>77</v>
       </c>
@@ -9239,7 +9242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>80</v>
       </c>
@@ -9253,7 +9256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>83</v>
       </c>
@@ -9267,7 +9270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>86</v>
       </c>
@@ -9281,7 +9284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>89</v>
       </c>
@@ -9295,7 +9298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>92</v>
       </c>
@@ -9309,7 +9312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>95</v>
       </c>
@@ -9323,7 +9326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>98</v>
       </c>
@@ -9337,7 +9340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>101</v>
       </c>
@@ -9351,7 +9354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>104</v>
       </c>
@@ -9365,7 +9368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>107</v>
       </c>
@@ -9379,7 +9382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>110</v>
       </c>
@@ -9393,7 +9396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>113</v>
       </c>
@@ -9407,7 +9410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>116</v>
       </c>
@@ -9421,7 +9424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>119</v>
       </c>
@@ -9435,7 +9438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>122</v>
       </c>
@@ -9449,7 +9452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>125</v>
       </c>
@@ -9463,7 +9466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>128</v>
       </c>
@@ -9477,7 +9480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>131</v>
       </c>
@@ -9491,7 +9494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>134</v>
       </c>
@@ -9505,7 +9508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>137</v>
       </c>
@@ -9519,7 +9522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>140</v>
       </c>
@@ -9533,7 +9536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>143</v>
       </c>
@@ -9547,7 +9550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>146</v>
       </c>
@@ -9561,7 +9564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>149</v>
       </c>
@@ -9575,7 +9578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>152</v>
       </c>
@@ -9589,7 +9592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>155</v>
       </c>
@@ -9603,7 +9606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>158</v>
       </c>
@@ -9617,7 +9620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>161</v>
       </c>
@@ -9631,7 +9634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>164</v>
       </c>
@@ -9645,7 +9648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>167</v>
       </c>
@@ -9659,7 +9662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>170</v>
       </c>
@@ -9673,7 +9676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>173</v>
       </c>
@@ -9687,7 +9690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>176</v>
       </c>
@@ -9701,7 +9704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>179</v>
       </c>
@@ -9715,7 +9718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>183</v>
       </c>
@@ -9729,7 +9732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>186</v>
       </c>
@@ -9743,7 +9746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>189</v>
       </c>
@@ -9757,7 +9760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>192</v>
       </c>
@@ -9771,7 +9774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>195</v>
       </c>
@@ -9785,7 +9788,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>199</v>
       </c>
@@ -9799,7 +9802,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>202</v>
       </c>
@@ -9813,7 +9816,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>205</v>
       </c>
@@ -9827,7 +9830,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>208</v>
       </c>
@@ -9841,7 +9844,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>212</v>
       </c>
@@ -9855,7 +9858,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>215</v>
       </c>
@@ -9869,7 +9872,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>219</v>
       </c>
@@ -9883,7 +9886,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>222</v>
       </c>
@@ -9897,7 +9900,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>225</v>
       </c>
@@ -9911,7 +9914,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>228</v>
       </c>
@@ -9925,7 +9928,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>231</v>
       </c>
@@ -9939,7 +9942,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>234</v>
       </c>
@@ -9953,7 +9956,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>237</v>
       </c>
@@ -9967,7 +9970,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>240</v>
       </c>
@@ -9981,7 +9984,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>243</v>
       </c>
@@ -9995,7 +9998,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>246</v>
       </c>
@@ -10009,7 +10012,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>249</v>
       </c>
@@ -10023,7 +10026,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>252</v>
       </c>
@@ -10037,7 +10040,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>255</v>
       </c>
@@ -10051,7 +10054,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>258</v>
       </c>
@@ -10065,7 +10068,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>261</v>
       </c>
@@ -10079,7 +10082,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>264</v>
       </c>
@@ -10093,7 +10096,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>267</v>
       </c>
@@ -10107,7 +10110,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>270</v>
       </c>
@@ -10121,7 +10124,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>273</v>
       </c>
@@ -10135,7 +10138,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>277</v>
       </c>
@@ -10149,7 +10152,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>280</v>
       </c>
@@ -10163,7 +10166,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>283</v>
       </c>
@@ -10177,7 +10180,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>286</v>
       </c>
@@ -10191,7 +10194,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>289</v>
       </c>
@@ -10205,7 +10208,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>292</v>
       </c>
@@ -10219,7 +10222,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>295</v>
       </c>
@@ -10233,7 +10236,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>298</v>
       </c>
@@ -10247,7 +10250,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>301</v>
       </c>
@@ -10261,7 +10264,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>304</v>
       </c>
@@ -10275,7 +10278,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>307</v>
       </c>
@@ -10289,7 +10292,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>310</v>
       </c>
@@ -10303,7 +10306,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>313</v>
       </c>
@@ -10317,7 +10320,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>316</v>
       </c>
@@ -10331,7 +10334,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>319</v>
       </c>
@@ -10345,7 +10348,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>322</v>
       </c>
@@ -10359,7 +10362,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>325</v>
       </c>
@@ -10373,7 +10376,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>328</v>
       </c>
@@ -10387,7 +10390,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>331</v>
       </c>
@@ -10401,7 +10404,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>334</v>
       </c>
@@ -10415,7 +10418,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>337</v>
       </c>
@@ -10429,7 +10432,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>340</v>
       </c>
@@ -10443,7 +10446,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>343</v>
       </c>
@@ -10457,7 +10460,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>346</v>
       </c>
@@ -10471,7 +10474,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>349</v>
       </c>
@@ -10485,7 +10488,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>352</v>
       </c>
@@ -10499,7 +10502,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>355</v>
       </c>
@@ -10513,7 +10516,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>358</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>361</v>
       </c>
@@ -10541,7 +10544,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>364</v>
       </c>
@@ -10555,7 +10558,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>367</v>
       </c>
@@ -10569,7 +10572,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>370</v>
       </c>
@@ -10583,7 +10586,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>373</v>
       </c>
@@ -10597,7 +10600,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>377</v>
       </c>
@@ -10611,7 +10614,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>380</v>
       </c>
@@ -10625,7 +10628,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>383</v>
       </c>
@@ -10639,7 +10642,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>386</v>
       </c>
@@ -10653,7 +10656,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>389</v>
       </c>
@@ -10667,7 +10670,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>392</v>
       </c>
@@ -10681,7 +10684,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>395</v>
       </c>
@@ -10695,7 +10698,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>398</v>
       </c>
@@ -10709,7 +10712,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>401</v>
       </c>
@@ -10723,7 +10726,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>404</v>
       </c>
@@ -10737,7 +10740,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>407</v>
       </c>
@@ -10751,7 +10754,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>410</v>
       </c>
@@ -10765,7 +10768,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>413</v>
       </c>
@@ -10779,7 +10782,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>416</v>
       </c>
@@ -10793,7 +10796,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>420</v>
       </c>
@@ -10807,7 +10810,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>423</v>
       </c>
@@ -10821,7 +10824,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>426</v>
       </c>
@@ -10835,7 +10838,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>429</v>
       </c>
@@ -10849,7 +10852,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>432</v>
       </c>
@@ -10863,7 +10866,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>435</v>
       </c>
@@ -10877,7 +10880,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>438</v>
       </c>
@@ -10891,7 +10894,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>441</v>
       </c>
@@ -10905,7 +10908,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>444</v>
       </c>
@@ -10919,7 +10922,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>447</v>
       </c>
@@ -10933,7 +10936,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>450</v>
       </c>
@@ -10947,7 +10950,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>453</v>
       </c>
@@ -10961,7 +10964,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>456</v>
       </c>
@@ -10975,7 +10978,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>459</v>
       </c>
@@ -10989,7 +10992,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>462</v>
       </c>
@@ -11003,7 +11006,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>465</v>
       </c>
@@ -11017,7 +11020,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>468</v>
       </c>
@@ -11031,7 +11034,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>471</v>
       </c>
@@ -11045,7 +11048,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>474</v>
       </c>
@@ -11059,7 +11062,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>477</v>
       </c>
@@ -11073,7 +11076,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>480</v>
       </c>
@@ -11087,7 +11090,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>483</v>
       </c>
@@ -11101,7 +11104,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>486</v>
       </c>
@@ -11115,7 +11118,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>489</v>
       </c>
@@ -11129,7 +11132,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>492</v>
       </c>
@@ -11143,7 +11146,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>495</v>
       </c>
@@ -11157,7 +11160,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>498</v>
       </c>
@@ -11171,7 +11174,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>501</v>
       </c>
@@ -11185,7 +11188,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>504</v>
       </c>
@@ -11199,7 +11202,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>507</v>
       </c>
@@ -11213,7 +11216,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>510</v>
       </c>
@@ -11227,7 +11230,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>513</v>
       </c>
@@ -11241,7 +11244,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>516</v>
       </c>
@@ -11255,7 +11258,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>519</v>
       </c>
@@ -11269,7 +11272,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>522</v>
       </c>
@@ -11283,7 +11286,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>525</v>
       </c>
@@ -11297,7 +11300,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>528</v>
       </c>
@@ -11311,7 +11314,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>531</v>
       </c>
@@ -11325,7 +11328,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>534</v>
       </c>
@@ -11339,7 +11342,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>537</v>
       </c>
@@ -11353,7 +11356,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>540</v>
       </c>
@@ -11367,7 +11370,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>543</v>
       </c>
@@ -11381,7 +11384,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>546</v>
       </c>
@@ -11395,7 +11398,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>549</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>552</v>
       </c>
@@ -11423,7 +11426,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>555</v>
       </c>
@@ -11437,7 +11440,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>558</v>
       </c>
@@ -11451,7 +11454,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>561</v>
       </c>
@@ -11465,7 +11468,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>564</v>
       </c>
@@ -11479,7 +11482,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>567</v>
       </c>
@@ -11493,7 +11496,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>570</v>
       </c>
@@ -11507,7 +11510,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>573</v>
       </c>
@@ -11521,7 +11524,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>576</v>
       </c>
@@ -11535,7 +11538,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>579</v>
       </c>
@@ -11549,7 +11552,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>582</v>
       </c>
@@ -11563,7 +11566,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>585</v>
       </c>
@@ -11577,7 +11580,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>588</v>
       </c>
@@ -11591,7 +11594,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="531" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>591</v>
       </c>
@@ -11605,7 +11608,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="532" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>594</v>
       </c>
@@ -11619,7 +11622,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="533" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>597</v>
       </c>
@@ -11633,7 +11636,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>600</v>
       </c>
@@ -11647,7 +11650,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="535" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>603</v>
       </c>
@@ -11661,7 +11664,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>606</v>
       </c>
@@ -11675,7 +11678,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="537" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>612</v>
       </c>
@@ -11689,7 +11692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="538" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>615</v>
       </c>
@@ -11703,7 +11706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>619</v>
       </c>
@@ -11717,7 +11720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>622</v>
       </c>
@@ -11731,7 +11734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>625</v>
       </c>
@@ -11745,7 +11748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>628</v>
       </c>
@@ -11759,7 +11762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>631</v>
       </c>
@@ -11773,7 +11776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="544" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>634</v>
       </c>
@@ -11787,7 +11790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>637</v>
       </c>
@@ -11801,7 +11804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="546" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>640</v>
       </c>
@@ -11815,7 +11818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>643</v>
       </c>
@@ -11829,7 +11832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>646</v>
       </c>
@@ -11843,7 +11846,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>649</v>
       </c>
@@ -11857,7 +11860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="550" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>652</v>
       </c>
@@ -11871,7 +11874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>655</v>
       </c>
@@ -11885,7 +11888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>658</v>
       </c>
@@ -11899,7 +11902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>661</v>
       </c>
@@ -11913,7 +11916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>664</v>
       </c>
@@ -11927,7 +11930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>667</v>
       </c>
@@ -11941,7 +11944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>670</v>
       </c>
@@ -11955,7 +11958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>673</v>
       </c>
@@ -11969,7 +11972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>676</v>
       </c>
@@ -11983,7 +11986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>679</v>
       </c>
@@ -11997,7 +12000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="560" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>682</v>
       </c>
@@ -12011,7 +12014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>685</v>
       </c>
@@ -12025,7 +12028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>688</v>
       </c>
@@ -12039,7 +12042,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>691</v>
       </c>
@@ -12053,7 +12056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>694</v>
       </c>
@@ -12067,7 +12070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>697</v>
       </c>
@@ -12081,7 +12084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>700</v>
       </c>
@@ -12095,7 +12098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>703</v>
       </c>
@@ -12109,7 +12112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>706</v>
       </c>
@@ -12123,7 +12126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>609</v>
       </c>
@@ -12137,7 +12140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>711</v>
       </c>
@@ -12151,7 +12154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>714</v>
       </c>
@@ -12165,7 +12168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="572" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>717</v>
       </c>
@@ -12179,7 +12182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>720</v>
       </c>
@@ -12193,7 +12196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>723</v>
       </c>
@@ -12207,7 +12210,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>726</v>
       </c>
@@ -12221,7 +12224,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>729</v>
       </c>
@@ -12235,7 +12238,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>732</v>
       </c>
@@ -12249,7 +12252,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="578" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>735</v>
       </c>
@@ -12263,7 +12266,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>738</v>
       </c>
@@ -12277,7 +12280,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="580" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>741</v>
       </c>
@@ -12291,7 +12294,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="581" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>744</v>
       </c>
@@ -12305,7 +12308,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>747</v>
       </c>
@@ -12319,7 +12322,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>750</v>
       </c>
@@ -12333,7 +12336,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="584" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>753</v>
       </c>
@@ -12347,7 +12350,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="585" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>756</v>
       </c>
@@ -12361,7 +12364,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>759</v>
       </c>
@@ -12375,7 +12378,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>762</v>
       </c>
@@ -12389,7 +12392,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>765</v>
       </c>
@@ -12403,7 +12406,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>768</v>
       </c>
@@ -12417,7 +12420,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>771</v>
       </c>
@@ -12431,7 +12434,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>774</v>
       </c>
@@ -12445,7 +12448,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="592" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>777</v>
       </c>
@@ -12459,7 +12462,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="593" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>780</v>
       </c>
@@ -12473,7 +12476,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>783</v>
       </c>
@@ -12487,7 +12490,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="595" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>786</v>
       </c>
@@ -12501,7 +12504,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="596" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>789</v>
       </c>
@@ -12515,7 +12518,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>792</v>
       </c>
@@ -12529,7 +12532,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>795</v>
       </c>
@@ -12543,7 +12546,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>798</v>
       </c>
@@ -12557,7 +12560,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>801</v>
       </c>
@@ -12571,7 +12574,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>804</v>
       </c>
@@ -12585,7 +12588,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="602" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>807</v>
       </c>
@@ -12599,7 +12602,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>810</v>
       </c>
@@ -12613,7 +12616,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>813</v>
       </c>
@@ -12627,7 +12630,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="605" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>816</v>
       </c>
@@ -12641,7 +12644,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="606" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>819</v>
       </c>
@@ -12655,7 +12658,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>822</v>
       </c>
@@ -12669,7 +12672,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>825</v>
       </c>
@@ -12683,7 +12686,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>828</v>
       </c>
@@ -12697,7 +12700,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>831</v>
       </c>
@@ -12711,7 +12714,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>834</v>
       </c>
@@ -12725,7 +12728,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="612" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>837</v>
       </c>
@@ -12739,7 +12742,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="613" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>840</v>
       </c>
@@ -12753,7 +12756,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="614" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>843</v>
       </c>
@@ -12767,7 +12770,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="615" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>846</v>
       </c>
@@ -12781,7 +12784,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>849</v>
       </c>
@@ -12795,7 +12798,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="617" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>852</v>
       </c>
@@ -12809,7 +12812,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>855</v>
       </c>
@@ -12823,7 +12826,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="619" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>858</v>
       </c>
@@ -12837,7 +12840,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="620" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>861</v>
       </c>
@@ -12851,7 +12854,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="621" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>864</v>
       </c>
@@ -12865,7 +12868,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>867</v>
       </c>
@@ -12879,7 +12882,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="623" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>870</v>
       </c>
@@ -12893,7 +12896,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>873</v>
       </c>
@@ -12907,7 +12910,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>876</v>
       </c>
@@ -12921,7 +12924,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>879</v>
       </c>
@@ -12935,7 +12938,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>882</v>
       </c>
@@ -12949,7 +12952,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>885</v>
       </c>
@@ -12963,7 +12966,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>888</v>
       </c>
@@ -12977,7 +12980,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>891</v>
       </c>
@@ -12991,7 +12994,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>989</v>
       </c>
@@ -13005,7 +13008,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>992</v>
       </c>
@@ -13019,7 +13022,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>995</v>
       </c>
@@ -13033,7 +13036,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="634" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>998</v>
       </c>
@@ -13047,7 +13050,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>1001</v>
       </c>
@@ -13061,7 +13064,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>1004</v>
       </c>
@@ -13075,7 +13078,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="637" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>1007</v>
       </c>
@@ -13089,7 +13092,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>1010</v>
       </c>
@@ -13103,7 +13106,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="639" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>894</v>
       </c>
@@ -13117,7 +13120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>897</v>
       </c>
@@ -13131,7 +13134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="641" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>1013</v>
       </c>
@@ -13145,7 +13148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>1016</v>
       </c>
@@ -13159,7 +13162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="643" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>1019</v>
       </c>
@@ -13173,7 +13176,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>1022</v>
       </c>
@@ -13187,7 +13190,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="645" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>1025</v>
       </c>
@@ -13201,7 +13204,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="646" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>1028</v>
       </c>
@@ -13215,7 +13218,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="647" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>1031</v>
       </c>
@@ -13229,7 +13232,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>1034</v>
       </c>
@@ -13243,7 +13246,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>1037</v>
       </c>
@@ -13257,7 +13260,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>1040</v>
       </c>
@@ -13271,7 +13274,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>1043</v>
       </c>
@@ -13285,7 +13288,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>1046</v>
       </c>
@@ -13299,7 +13302,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>1049</v>
       </c>
@@ -13313,7 +13316,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>1052</v>
       </c>
@@ -13327,7 +13330,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>1055</v>
       </c>
@@ -13341,7 +13344,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="656" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>1058</v>
       </c>
@@ -13355,7 +13358,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>1061</v>
       </c>
@@ -13369,7 +13372,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="658" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>1064</v>
       </c>
@@ -13383,7 +13386,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="659" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>1067</v>
       </c>
@@ -13397,7 +13400,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="660" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>1070</v>
       </c>
@@ -13411,7 +13414,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>1073</v>
       </c>
@@ -13425,7 +13428,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>1076</v>
       </c>
@@ -13439,7 +13442,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="663" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>1079</v>
       </c>
@@ -13453,7 +13456,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>1082</v>
       </c>
@@ -13467,7 +13470,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="665" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>1085</v>
       </c>
@@ -13481,7 +13484,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="666" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>1088</v>
       </c>
@@ -13495,7 +13498,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>914</v>
       </c>
@@ -13509,7 +13512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>919</v>
       </c>
@@ -13523,7 +13526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>1095</v>
       </c>
@@ -13537,7 +13540,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>1098</v>
       </c>
@@ -13551,7 +13554,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>1101</v>
       </c>
@@ -13565,7 +13568,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>1104</v>
       </c>
@@ -13579,7 +13582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="673" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>926</v>
       </c>
@@ -13593,7 +13596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>1109</v>
       </c>
@@ -13607,7 +13610,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>1112</v>
       </c>
@@ -13621,7 +13624,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="676" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>935</v>
       </c>
@@ -13635,7 +13638,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1117</v>
       </c>
@@ -13649,7 +13652,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1120</v>
       </c>
@@ -13663,7 +13666,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1123</v>
       </c>
@@ -13677,7 +13680,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1126</v>
       </c>
@@ -13691,7 +13694,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1129</v>
       </c>
@@ -13705,7 +13708,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1132</v>
       </c>
@@ -13719,7 +13722,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="683" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1135</v>
       </c>
@@ -13733,7 +13736,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="684" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1138</v>
       </c>
@@ -13747,7 +13750,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="685" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1141</v>
       </c>
@@ -13761,7 +13764,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="686" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1144</v>
       </c>
@@ -13775,7 +13778,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="687" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1147</v>
       </c>
@@ -13789,7 +13792,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="688" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1150</v>
       </c>
@@ -13803,7 +13806,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="689" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1153</v>
       </c>
@@ -13817,7 +13820,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="690" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1156</v>
       </c>
@@ -13831,7 +13834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1159</v>
       </c>
@@ -13845,7 +13848,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="692" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1162</v>
       </c>
@@ -13859,7 +13862,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1165</v>
       </c>
@@ -13873,7 +13876,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="694" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1168</v>
       </c>
@@ -13887,7 +13890,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1171</v>
       </c>
@@ -13901,7 +13904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="696" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1174</v>
       </c>
@@ -13915,7 +13918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="697" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1177</v>
       </c>
@@ -13929,7 +13932,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="698" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1180</v>
       </c>
@@ -13943,7 +13946,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1183</v>
       </c>
@@ -13957,7 +13960,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="700" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1186</v>
       </c>
@@ -13971,7 +13974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="701" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>176</v>
       </c>
@@ -13985,7 +13988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="702" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>277</v>
       </c>
@@ -13999,7 +14002,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="703" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1193</v>
       </c>
@@ -14013,7 +14016,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="704" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1156</v>
       </c>
@@ -14027,7 +14030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="705" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1165</v>
       </c>
@@ -14041,7 +14044,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="706" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1200</v>
       </c>
@@ -14055,7 +14058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="707" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1203</v>
       </c>
@@ -14069,7 +14072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1206</v>
       </c>
@@ -14083,7 +14086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="709" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1209</v>
       </c>
@@ -14097,7 +14100,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="710" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1212</v>
       </c>
@@ -14111,7 +14114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="711" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1215</v>
       </c>
@@ -14125,7 +14128,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="712" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1168</v>
       </c>
@@ -14139,7 +14142,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1220</v>
       </c>
@@ -14153,7 +14156,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="714" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1223</v>
       </c>
@@ -14167,7 +14170,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1226</v>
       </c>
@@ -14181,7 +14184,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="716" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1229</v>
       </c>
@@ -14195,7 +14198,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="717" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1109</v>
       </c>
@@ -14209,7 +14212,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="718" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1234</v>
       </c>
@@ -14223,7 +14226,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1209</v>
       </c>
@@ -14237,7 +14240,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="720" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1079</v>
       </c>
@@ -14251,7 +14254,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="721" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1241</v>
       </c>
@@ -14265,7 +14268,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="722" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1244</v>
       </c>
@@ -14279,7 +14282,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1247</v>
       </c>
@@ -14293,7 +14296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1250</v>
       </c>
@@ -14307,7 +14310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="725" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1253</v>
       </c>
@@ -14317,7 +14320,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="726" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1254</v>
       </c>
@@ -14327,11 +14330,13 @@
         <v>419</v>
       </c>
     </row>
-    <row r="727" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B727" s="3"/>
+      <c r="B727" s="2" t="s">
+        <v>1256</v>
+      </c>
       <c r="C727" s="3"/>
       <c r="D727" s="2" t="s">
         <v>419</v>
